--- a/extenbooks/S1503_extenbook.xlsx
+++ b/extenbooks/S1503_extenbook.xlsx
@@ -7151,7 +7151,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -8216,11 +8216,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8243,64 +8243,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chapter 15 series S1503</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1503_research.json", "adequacy_report": "Technical/docs/chapters/CH15_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1503_DPR.md", "epr": "Technical/docs/series/S1503_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1503_load.py", "processor": "Technical/code/P02_processors/P02_S1503_construct.py", "validator": "Technical/code/V03_validators/V03_S1503_validate.py", "processed": "Technical/data/processed/S1503.parquet", "chopped_csv": "Technical/chopped/S1503.csv", "extenbook_xlsx": "Technical/extenbooks/S1503_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1503_extenbook.xlsx
+++ b/extenbooks/S1503_extenbook.xlsx
@@ -880,7 +880,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -7137,7 +7137,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Pipeline stage**: Ingestion</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -7336,54 +7336,58 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Rate (decimal log-difference).</t>
+          <t>Rate (decimal annual **simple percent change**): `g_i(t) = (YR_i(t) - YR_i(t-1)) / YR_i(t-1)`, same as S1502</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>(§1/§4 above). Registry/chopped units string: `decimal_annual_growth_rate`. NOT a log-difference —</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>hand-verified on S1502 DURMFG 1988 = 0.063481 = simple percent change (log-diff would be 0.061547).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Units label corrected from `rate_decimal_log_diff` in remediation T1.7 (C567, 2026-07-01).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Same as S1502. Information-sector reaggregation and Federal Government NIPA reclassification are post-2010 splice hazards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Same as S1502. Information-sector reaggregation and Federal Government National Income and Product Accounts (NIPA) reclassification are post-2010 splice hazards.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>- **CD legacy ID**: `S078`</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figures 15.2-15.3; Appendix 15.1 p. 895</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
@@ -7393,127 +7397,144 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>- **Predecessor-build ID**: `S078`</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figures 15.2-15.3; Appendix 15.1 p. 895</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Tolerance +/- 1.0% per (year, industry) vs the book's "Calculated Growth Rate" columns. Expected MAE: near zero.</t>
-        </is>
-      </c>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Tolerance +/- 1.0% per (year, industry) vs the book's "Calculated Growth Rate" columns. Expected mean absolute error (MAE): near zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4">
         <f>== EPR: S1503_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t># S1503 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>**Series**: S1503 — Growth Rates of Real Output, US Major Industries (Panel B)</t>
-        </is>
-      </c>
-    </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t># S1503 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `formula`</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>**Extension method**: identical to S1502 — re-fetch BEA Chain-Type Quantity Indexes, recompute log-differences for services &amp; government industries</t>
+          <t>**Series**: S1503 — Growth Rates of Real Output, US Major Industries (Panel B)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Pipeline stage**: Extension</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Construction classification**: `formula`</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>**Extension method**: identical to S1502 — re-fetch BEA Chain-Type Quantity Indexes, recompute simple-percent-change growth rates (the book's convention) for services &amp; government industries</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Identical methodology to S1502 EPR. See `S1502_EPR.md` for full discussion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-    </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Specific to Panel B:</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>- Information sector definition changed in 2017 BEA vintage (NAICS revision merged some publishing/broadcasting sub-codes); post-2017 splice flagged.</t>
+          <t>Identical methodology to S1502 EPR. See `S1502_EPR.md` for full discussion.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>- Federal Government NIPA reclassification ~2018 (BEA changed how military pay is allocated between consumption and gross investment); per-vintage notes in loader.</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Specific to Panel B:</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
+        <is>
+          <t>- Information sector definition changed in 2017 BEA vintage (North American Industry Classification System (NAICS) revision merged some publishing/broadcasting sub-codes); post-2017 splice flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>- Federal Government National Income and Product Accounts (NIPA) reclassification ~2018 (BEA changed how military pay is allocated between consumption and gross investment); per-vintage notes in loader.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>No proxies, no synthetic data, BEA Industry remains the same source as Shaikh used.</t>
         </is>
@@ -8201,7 +8222,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:14:07.913664+00:00</t>
+          <t>2026-07-02T06:19:37.431806+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1503_extenbook.xlsx
+++ b/extenbooks/S1503_extenbook.xlsx
@@ -8222,7 +8222,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:19:37.431806+00:00</t>
+          <t>2026-07-11T03:44:23.317227+00:00</t>
         </is>
       </c>
     </row>
@@ -8237,11 +8237,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8264,6 +8264,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BEA_GDP_BY_INDUSTRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful formula replication of book figure 15.2B (services and government industries panel), companion to S1502. Simple-percent-change growth rates (hand-verified: DURMFG 1988 = 0.063481 = simple pct, not log-diff) of BEA real value added by industry, 1988-2010 (book caption reads 1987-2010; 1988 is the first valid growth year - documented). Units decimal_annual_growth_rate consistent.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1503_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1503_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>decimal_annual_growth_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
